--- a/docs/shows/shows.xlsx
+++ b/docs/shows/shows.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/milesshultz/Documents/kings_website/rock/docs/shows/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2B11E2F6-4300-D346-96C5-1F99D0D2C0D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE78DDE7-2F78-5345-8902-07F3E8ED1CBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Shows" sheetId="2" r:id="rId1"/>
-    <sheet name="How To Use" sheetId="1" r:id="rId2"/>
+    <sheet name="Shows" sheetId="1" r:id="rId1"/>
+    <sheet name="How To Use" sheetId="2" r:id="rId2"/>
     <sheet name="Column Guide" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
@@ -22,7 +22,213 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="110">
+  <si>
+    <t>HOW TO ADD A SHOW: Fill in a new row below. Date format: YYYY-MM-DD. Cancelled: TRUE or FALSE. Leave optional columns blank if not needed. After saving, run:  python scripts/update_shows.py  then commit &amp; push.</t>
+  </si>
+  <si>
+    <t>Date
+(YYYY-MM-DD)</t>
+  </si>
+  <si>
+    <t>Venue Name</t>
+  </si>
+  <si>
+    <t>Venue URL
+(optional)</t>
+  </si>
+  <si>
+    <t>Detail
+(time · location)</t>
+  </si>
+  <si>
+    <t>Detail Link Name
+(optional)</t>
+  </si>
+  <si>
+    <t>Detail Link URL
+(optional)</t>
+  </si>
+  <si>
+    <t>Detail Link Suffix
+(optional)</t>
+  </si>
+  <si>
+    <t>Description
+(optional)</t>
+  </si>
+  <si>
+    <t>Cancelled
+(TRUE/FALSE)</t>
+  </si>
+  <si>
+    <t>2023-09-09</t>
+  </si>
+  <si>
+    <t>Ewing Block Party</t>
+  </si>
+  <si>
+    <t>2024-04-26</t>
+  </si>
+  <si>
+    <t>Lincolnwood Spring Fling</t>
+  </si>
+  <si>
+    <t>PTA Spring Fling</t>
+  </si>
+  <si>
+    <t>2024-06-07</t>
+  </si>
+  <si>
+    <t>Fat Shallot</t>
+  </si>
+  <si>
+    <t>https://www.thefatshallot.com/the-fat-shallots-new-site-is-coming-soon/</t>
+  </si>
+  <si>
+    <t>2024-07-21</t>
+  </si>
+  <si>
+    <t>Chicago Union</t>
+  </si>
+  <si>
+    <t>https://watchufa.com/union</t>
+  </si>
+  <si>
+    <t>2024-08-17</t>
+  </si>
+  <si>
+    <t>Private Party</t>
+  </si>
+  <si>
+    <t>2024-08-24</t>
+  </si>
+  <si>
+    <t>2024-09-07</t>
+  </si>
+  <si>
+    <t>2024-10-09</t>
+  </si>
+  <si>
+    <t>Covenant Nursery School</t>
+  </si>
+  <si>
+    <t>https://www.covenantnurseryschool.org/</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Dining for Dollars</t>
+  </si>
+  <si>
+    <t>2025-04-03</t>
+  </si>
+  <si>
+    <t>2025-06-07</t>
+  </si>
+  <si>
+    <t>2025-06-25</t>
+  </si>
+  <si>
+    <t>American Legion Post 42</t>
+  </si>
+  <si>
+    <t>https://www.evanstonpost42.com/</t>
+  </si>
+  <si>
+    <t>2025-09-06</t>
+  </si>
+  <si>
+    <t>2025-10-10</t>
+  </si>
+  <si>
+    <t>Ackerman Park</t>
+  </si>
+  <si>
+    <t>Invest in Neighborhood Schools</t>
+  </si>
+  <si>
+    <t>https://www.investinevanston.com/</t>
+  </si>
+  <si>
+    <t>2025-10-18</t>
+  </si>
+  <si>
+    <t>Mack's Bike &amp; Goods</t>
+  </si>
+  <si>
+    <t>https://www.macksbikeandgoods.com/</t>
+  </si>
+  <si>
+    <t>Fall Fest</t>
+  </si>
+  <si>
+    <t>TRUE</t>
+  </si>
+  <si>
+    <t>2025-11-16</t>
+  </si>
+  <si>
+    <t>Double Clutch</t>
+  </si>
+  <si>
+    <t>https://www.doubleclutchbrewing.com/</t>
+  </si>
+  <si>
+    <t>2026-01-24</t>
+  </si>
+  <si>
+    <t>Goat Village</t>
+  </si>
+  <si>
+    <t>https://www.goatvillage777.com/</t>
+  </si>
+  <si>
+    <t>2026-04-24</t>
+  </si>
+  <si>
+    <t>D65 One Fund Spring Cha Ching</t>
+  </si>
+  <si>
+    <t>2026-05-14</t>
+  </si>
+  <si>
+    <t>5:30 PM</t>
+  </si>
+  <si>
+    <t>2026-05-16</t>
+  </si>
+  <si>
+    <t>7:00 PM</t>
+  </si>
+  <si>
+    <t>2026-06-21</t>
+  </si>
+  <si>
+    <t>5:00 PM · ETHS Lazier Field</t>
+  </si>
+  <si>
+    <t>Pre-game set before the Chicago Union — a pro Ultimate Frisbee Association (UFA) team — takes the field.</t>
+  </si>
+  <si>
+    <t>2026-06-24</t>
+  </si>
+  <si>
+    <t>Ridgeville Parks District</t>
+  </si>
+  <si>
+    <t>https://ridgevilleparks.myrec.com/info/activities/program_details.aspx?ProgramID=29893</t>
+  </si>
+  <si>
+    <t>6:00 PM</t>
+  </si>
+  <si>
+    <t>Part of the Ridgeville Parks District "Concerts on the Ridge" summer series.</t>
+  </si>
+  <si>
+    <t>2026-09-12</t>
+  </si>
+  <si>
+    <t>4:00 PM</t>
+  </si>
   <si>
     <t>How To Add a New Show</t>
   </si>
@@ -77,209 +283,6 @@
 4. Click Commit to main.
 5. Click Push origin (top right).
 GitHub Pages rebuilds in under a minute — check kingsofewing.com/#shows to confirm.</t>
-  </si>
-  <si>
-    <t>HOW TO ADD A SHOW: Fill in a new row below. Date format: YYYY-MM-DD. Cancelled: TRUE or FALSE. Leave optional columns blank if not needed. After saving, run:  python scripts/update_shows.py  then commit &amp; push.</t>
-  </si>
-  <si>
-    <t>Date
-(YYYY-MM-DD)</t>
-  </si>
-  <si>
-    <t>Venue Name</t>
-  </si>
-  <si>
-    <t>Venue URL
-(optional)</t>
-  </si>
-  <si>
-    <t>Detail
-(time · location)</t>
-  </si>
-  <si>
-    <t>Detail Link Name
-(optional)</t>
-  </si>
-  <si>
-    <t>Detail Link URL
-(optional)</t>
-  </si>
-  <si>
-    <t>Detail Link Suffix
-(optional)</t>
-  </si>
-  <si>
-    <t>Description
-(optional)</t>
-  </si>
-  <si>
-    <t>Cancelled
-(TRUE/FALSE)</t>
-  </si>
-  <si>
-    <t>2026-06-21</t>
-  </si>
-  <si>
-    <t>Chicago Union</t>
-  </si>
-  <si>
-    <t>https://watchufa.com/union</t>
-  </si>
-  <si>
-    <t>5:00 PM · ETHS Lazier Field</t>
-  </si>
-  <si>
-    <t>Pre-game set before the Chicago Union — a pro Ultimate Frisbee Association (UFA) team — takes the field.</t>
-  </si>
-  <si>
-    <t>2026-06-24</t>
-  </si>
-  <si>
-    <t>Ridgeville Parks District</t>
-  </si>
-  <si>
-    <t>https://ridgevilleparks.myrec.com/info/activities/program_details.aspx?ProgramID=29893</t>
-  </si>
-  <si>
-    <t>6:00 PM</t>
-  </si>
-  <si>
-    <t>Part of the Ridgeville Parks District "Concerts on the Ridge" summer series.</t>
-  </si>
-  <si>
-    <t>2026-09-12</t>
-  </si>
-  <si>
-    <t>Ewing Block Party</t>
-  </si>
-  <si>
-    <t>2026-05-14</t>
-  </si>
-  <si>
-    <t>Fat Shallot</t>
-  </si>
-  <si>
-    <t>https://www.thefatshallot.com/the-fat-shallots-new-site-is-coming-soon/</t>
-  </si>
-  <si>
-    <t>5:30 PM</t>
-  </si>
-  <si>
-    <t>Covenant Nursery School</t>
-  </si>
-  <si>
-    <t>https://www.covenantnurseryschool.org/</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Dining for Dollars</t>
-  </si>
-  <si>
-    <t>2026-05-16</t>
-  </si>
-  <si>
-    <t>Private Party</t>
-  </si>
-  <si>
-    <t>7:00 PM</t>
-  </si>
-  <si>
-    <t>2026-04-24</t>
-  </si>
-  <si>
-    <t>American Legion Post 42</t>
-  </si>
-  <si>
-    <t>https://www.evanstonpost42.com/</t>
-  </si>
-  <si>
-    <t>D65 One Fund Spring Cha Ching</t>
-  </si>
-  <si>
-    <t>2026-01-24</t>
-  </si>
-  <si>
-    <t>Goat Village</t>
-  </si>
-  <si>
-    <t>https://www.goatvillage777.com/</t>
-  </si>
-  <si>
-    <t>2025-11-16</t>
-  </si>
-  <si>
-    <t>Double Clutch</t>
-  </si>
-  <si>
-    <t>https://www.doubleclutchbrewing.com/</t>
-  </si>
-  <si>
-    <t>2025-10-18</t>
-  </si>
-  <si>
-    <t>Mack's Bike &amp; Goods</t>
-  </si>
-  <si>
-    <t>https://www.macksbikeandgoods.com/</t>
-  </si>
-  <si>
-    <t>Fall Fest</t>
-  </si>
-  <si>
-    <t>TRUE</t>
-  </si>
-  <si>
-    <t>2025-10-10</t>
-  </si>
-  <si>
-    <t>Ackerman Park</t>
-  </si>
-  <si>
-    <t>Invest in Neighborhood Schools</t>
-  </si>
-  <si>
-    <t>https://www.investinevanston.com/</t>
-  </si>
-  <si>
-    <t>2025-09-06</t>
-  </si>
-  <si>
-    <t>2025-06-25</t>
-  </si>
-  <si>
-    <t>2025-06-07</t>
-  </si>
-  <si>
-    <t>2025-04-03</t>
-  </si>
-  <si>
-    <t>Lincolnwood Spring Fling</t>
-  </si>
-  <si>
-    <t>PTA Spring Fling</t>
-  </si>
-  <si>
-    <t>2024-10-09</t>
-  </si>
-  <si>
-    <t>2024-09-07</t>
-  </si>
-  <si>
-    <t>2024-08-24</t>
-  </si>
-  <si>
-    <t>2024-08-17</t>
-  </si>
-  <si>
-    <t>2024-07-21</t>
-  </si>
-  <si>
-    <t>2024-06-07</t>
-  </si>
-  <si>
-    <t>2024-04-26</t>
-  </si>
-  <si>
-    <t>2023-09-09</t>
   </si>
   <si>
     <t>Column</t>
@@ -489,7 +492,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -524,11 +527,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF3D3020"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -537,16 +549,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
@@ -559,18 +561,31 @@
     <xf numFmtId="0" fontId="9" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="20" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -874,460 +889,460 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16" style="4" customWidth="1"/>
-    <col min="2" max="2" width="30.83203125" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="104.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="35.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="37" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="46.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="23.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="129.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.1640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.83203125" style="4" customWidth="1"/>
-    <col min="11" max="16384" width="8.83203125" style="4"/>
+    <col min="1" max="1" width="18" style="13" customWidth="1"/>
+    <col min="2" max="2" width="30.83203125" style="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="104.5" style="13" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="35.6640625" style="13" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="37" style="13" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="46.5" style="13" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23.6640625" style="13" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="129.6640625" style="13" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.1640625" style="13" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="8.83203125" style="13" customWidth="1"/>
+    <col min="12" max="16384" width="8.83203125" style="13"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="12"/>
+      <c r="I1" s="12"/>
+    </row>
+    <row r="2" spans="1:9" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2" s="14" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
+      <c r="H3" s="16"/>
+      <c r="I3" s="17"/>
+    </row>
+    <row r="4" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
-      <c r="I1" s="13"/>
-    </row>
-    <row r="2" spans="1:9" ht="54" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
+      <c r="B4" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="C4" s="16"/>
+      <c r="D4" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="E4" s="16"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="16"/>
+      <c r="H4" s="16"/>
+      <c r="I4" s="17"/>
+    </row>
+    <row r="5" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="B5" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="C5" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="16"/>
+      <c r="H5" s="16"/>
+      <c r="I5" s="17"/>
+    </row>
+    <row r="6" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="B6" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="C6" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="16"/>
+      <c r="H6" s="16"/>
+      <c r="I6" s="17"/>
+    </row>
+    <row r="7" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="15" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
+      <c r="B7" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="C7" s="16"/>
+      <c r="D7" s="16"/>
+      <c r="E7" s="16"/>
+      <c r="F7" s="16"/>
+      <c r="G7" s="16"/>
+      <c r="H7" s="16"/>
+      <c r="I7" s="17"/>
+    </row>
+    <row r="8" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="B8" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" s="16"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="16"/>
+      <c r="I8" s="17"/>
+    </row>
+    <row r="9" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="B9" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="16"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="16"/>
+      <c r="I9" s="17"/>
+    </row>
+    <row r="10" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
-      <c r="G3" s="7"/>
-      <c r="H3" s="7" t="s">
+      <c r="B10" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="16"/>
+      <c r="E10" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="I3" s="6"/>
-    </row>
-    <row r="4" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
+      <c r="F10" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="G10" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="H10" s="16"/>
+      <c r="I10" s="17"/>
+    </row>
+    <row r="11" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="B11" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11" s="16"/>
+      <c r="D11" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="E11" s="16"/>
+      <c r="F11" s="16"/>
+      <c r="G11" s="16"/>
+      <c r="H11" s="16"/>
+      <c r="I11" s="17"/>
+    </row>
+    <row r="12" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7" t="s">
+      <c r="B12" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="D12" s="16"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="16"/>
+      <c r="H12" s="16"/>
+      <c r="I12" s="17"/>
+    </row>
+    <row r="13" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="I4" s="6"/>
-    </row>
-    <row r="5" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
+      <c r="B13" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="C13" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
-      <c r="I5" s="6"/>
-    </row>
-    <row r="6" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
+      <c r="D13" s="16"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="16"/>
+      <c r="G13" s="16"/>
+      <c r="H13" s="16"/>
+      <c r="I13" s="17"/>
+    </row>
+    <row r="14" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B14" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="16"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="16"/>
+      <c r="G14" s="16"/>
+      <c r="H14" s="16"/>
+      <c r="I14" s="17"/>
+    </row>
+    <row r="15" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="B15" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="C15" s="16"/>
+      <c r="D15" s="16"/>
+      <c r="E15" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="F15" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="G15" s="16"/>
+      <c r="H15" s="16"/>
+      <c r="I15" s="17"/>
+    </row>
+    <row r="16" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="G6" s="7" t="s">
+      <c r="B16" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="H6" s="7"/>
-      <c r="I6" s="6"/>
-    </row>
-    <row r="7" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="6" t="s">
+      <c r="C16" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="D16" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7" t="s">
+      <c r="E16" s="16"/>
+      <c r="F16" s="16"/>
+      <c r="G16" s="16"/>
+      <c r="H16" s="16"/>
+      <c r="I16" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="7"/>
-      <c r="I7" s="6"/>
-    </row>
-    <row r="8" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="s">
+    </row>
+    <row r="17" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B17" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C17" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D17" s="16"/>
+      <c r="E17" s="16"/>
+      <c r="F17" s="16"/>
+      <c r="G17" s="16"/>
+      <c r="H17" s="16"/>
+      <c r="I17" s="17"/>
+    </row>
+    <row r="18" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
-      <c r="I8" s="6"/>
-    </row>
-    <row r="9" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="6" t="s">
+      <c r="B18" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="C18" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="D18" s="16"/>
+      <c r="E18" s="16"/>
+      <c r="F18" s="16"/>
+      <c r="G18" s="16"/>
+      <c r="H18" s="16"/>
+      <c r="I18" s="17"/>
+    </row>
+    <row r="19" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="7"/>
-      <c r="I9" s="6"/>
-    </row>
-    <row r="10" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="6" t="s">
+      <c r="B19" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="C19" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="D19" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="E19" s="16"/>
+      <c r="F19" s="16"/>
+      <c r="G19" s="16"/>
+      <c r="H19" s="16"/>
+      <c r="I19" s="17"/>
+    </row>
+    <row r="20" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="B20" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="D20" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="7"/>
-      <c r="I10" s="6"/>
-    </row>
-    <row r="11" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="s">
+      <c r="E20" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="F20" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="G20" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="H20" s="16"/>
+      <c r="I20" s="17"/>
+    </row>
+    <row r="21" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B21" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="C21" s="16"/>
+      <c r="D21" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="E21" s="16"/>
+      <c r="F21" s="16"/>
+      <c r="G21" s="16"/>
+      <c r="H21" s="16"/>
+      <c r="I21" s="17"/>
+    </row>
+    <row r="22" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="B22" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="C22" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
-      <c r="I11" s="6" t="s">
+      <c r="E22" s="16"/>
+      <c r="F22" s="16"/>
+      <c r="G22" s="16"/>
+      <c r="H22" s="16" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="s">
+      <c r="I22" s="17"/>
+    </row>
+    <row r="23" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B23" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7" t="s">
+      <c r="C23" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="F12" s="7" t="s">
+      <c r="D23" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="G12" s="7"/>
-      <c r="H12" s="7"/>
-      <c r="I12" s="6"/>
-    </row>
-    <row r="13" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="s">
+      <c r="E23" s="16"/>
+      <c r="F23" s="16"/>
+      <c r="G23" s="16"/>
+      <c r="H23" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="B13" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="7"/>
-      <c r="I13" s="6"/>
-    </row>
-    <row r="14" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="s">
+      <c r="I23" s="17"/>
+    </row>
+    <row r="24" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="B14" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7"/>
-      <c r="H14" s="7"/>
-      <c r="I14" s="6"/>
-    </row>
-    <row r="15" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="6" t="s">
+      <c r="B24" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="16"/>
+      <c r="D24" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="B15" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
-      <c r="G15" s="7"/>
-      <c r="H15" s="7"/>
-      <c r="I15" s="6"/>
-    </row>
-    <row r="16" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
-      <c r="I16" s="6"/>
-    </row>
-    <row r="17" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="F17" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="G17" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="H17" s="7"/>
-      <c r="I17" s="6"/>
-    </row>
-    <row r="18" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7"/>
-      <c r="H18" s="7"/>
-      <c r="I18" s="6"/>
-    </row>
-    <row r="19" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="7"/>
-      <c r="G19" s="7"/>
-      <c r="H19" s="7"/>
-      <c r="I19" s="6"/>
-    </row>
-    <row r="20" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="B20" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="7"/>
-      <c r="G20" s="7"/>
-      <c r="H20" s="7"/>
-      <c r="I20" s="6"/>
-    </row>
-    <row r="21" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="B21" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="7"/>
-      <c r="G21" s="7"/>
-      <c r="H21" s="7"/>
-      <c r="I21" s="6"/>
-    </row>
-    <row r="22" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="B22" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="7"/>
-      <c r="G22" s="7"/>
-      <c r="H22" s="7"/>
-      <c r="I22" s="6"/>
-    </row>
-    <row r="23" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="B23" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="E23" s="7"/>
-      <c r="F23" s="7"/>
-      <c r="G23" s="7"/>
-      <c r="H23" s="7"/>
-      <c r="I23" s="6"/>
-    </row>
-    <row r="24" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="B24" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="C24" s="7"/>
-      <c r="D24" s="17">
-        <v>0.16666666666666666</v>
-      </c>
-      <c r="E24" s="7"/>
-      <c r="F24" s="7"/>
-      <c r="G24" s="7"/>
-      <c r="H24" s="7"/>
-      <c r="I24" s="6"/>
+      <c r="E24" s="16"/>
+      <c r="F24" s="16"/>
+      <c r="G24" s="16"/>
+      <c r="H24" s="16"/>
+      <c r="I24" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1338,7 +1353,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
@@ -1347,64 +1362,64 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="15"/>
+      <c r="A1" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="B1" s="9"/>
     </row>
     <row r="2" spans="1:2" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="15"/>
+      <c r="A2" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="B2" s="9"/>
     </row>
     <row r="3" spans="1:2" ht="8" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="8"/>
-      <c r="B3" s="8"/>
+      <c r="A3" s="4"/>
+      <c r="B3" s="4"/>
     </row>
     <row r="4" spans="1:2" ht="84" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>3</v>
+      <c r="A4" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>5</v>
+      <c r="A5" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>7</v>
+      <c r="A6" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="140" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>9</v>
+      <c r="A7" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="126" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" s="10" t="s">
-        <v>11</v>
+      <c r="A8" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A9" s="8"/>
-      <c r="B9" s="8"/>
+      <c r="A9" s="4"/>
+      <c r="B9" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1428,142 +1443,142 @@
   <sheetData>
     <row r="1" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>

--- a/docs/shows/shows.xlsx
+++ b/docs/shows/shows.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/milesshultz/Documents/kings_website/rock/docs/shows/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE78DDE7-2F78-5345-8902-07F3E8ED1CBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{25EF77C3-CC6A-0244-B57E-1E573E19DF43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="109">
   <si>
     <t>HOW TO ADD A SHOW: Fill in a new row below. Date format: YYYY-MM-DD. Cancelled: TRUE or FALSE. Leave optional columns blank if not needed. After saving, run:  python scripts/update_shows.py  then commit &amp; push.</t>
   </si>
@@ -225,9 +225,6 @@
   </si>
   <si>
     <t>2026-09-12</t>
-  </si>
-  <si>
-    <t>4:00 PM</t>
   </si>
   <si>
     <t>How To Add a New Show</t>
@@ -561,32 +558,32 @@
     <xf numFmtId="0" fontId="9" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -893,456 +890,456 @@
   <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18" style="13" customWidth="1"/>
-    <col min="2" max="2" width="30.83203125" style="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="104.5" style="13" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="35.6640625" style="13" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="37" style="13" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="46.5" style="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="23.6640625" style="13" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="129.6640625" style="13" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.1640625" style="13" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="8.83203125" style="13" customWidth="1"/>
-    <col min="12" max="16384" width="8.83203125" style="13"/>
+    <col min="1" max="1" width="18" style="8" customWidth="1"/>
+    <col min="2" max="2" width="30.83203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="104.5" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="35.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="37" style="8" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="46.5" style="8" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="129.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.1640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="8.83203125" style="8" customWidth="1"/>
+    <col min="12" max="16384" width="8.83203125" style="8"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="12"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
     </row>
     <row r="2" spans="1:9" ht="54" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="C2" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="14" t="s">
+      <c r="D2" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="14" t="s">
+      <c r="E2" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="14" t="s">
+      <c r="F2" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="14" t="s">
+      <c r="G2" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="14" t="s">
+      <c r="H2" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="14" t="s">
+      <c r="I2" s="9" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="15" t="s">
+      <c r="A3" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="16" t="s">
+      <c r="B3" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="16"/>
-      <c r="D3" s="16"/>
-      <c r="E3" s="16"/>
-      <c r="F3" s="16"/>
-      <c r="G3" s="16"/>
-      <c r="H3" s="16"/>
-      <c r="I3" s="17"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="11"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="12"/>
     </row>
     <row r="4" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="16" t="s">
+      <c r="B4" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="16"/>
-      <c r="D4" s="16" t="s">
+      <c r="C4" s="11"/>
+      <c r="D4" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="16"/>
-      <c r="F4" s="16"/>
-      <c r="G4" s="16"/>
-      <c r="H4" s="16"/>
-      <c r="I4" s="17"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="11"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="12"/>
     </row>
     <row r="5" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="16" t="s">
+      <c r="C5" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
-      <c r="F5" s="16"/>
-      <c r="G5" s="16"/>
-      <c r="H5" s="16"/>
-      <c r="I5" s="17"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="12"/>
     </row>
     <row r="6" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="16" t="s">
+      <c r="C6" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16"/>
-      <c r="F6" s="16"/>
-      <c r="G6" s="16"/>
-      <c r="H6" s="16"/>
-      <c r="I6" s="17"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="12"/>
     </row>
     <row r="7" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="15" t="s">
+      <c r="A7" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="16" t="s">
+      <c r="B7" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="C7" s="16"/>
-      <c r="D7" s="16"/>
-      <c r="E7" s="16"/>
-      <c r="F7" s="16"/>
-      <c r="G7" s="16"/>
-      <c r="H7" s="16"/>
-      <c r="I7" s="17"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="11"/>
+      <c r="H7" s="11"/>
+      <c r="I7" s="12"/>
     </row>
     <row r="8" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="15" t="s">
+      <c r="A8" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="16" t="s">
+      <c r="B8" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="16" t="s">
+      <c r="C8" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="D8" s="16"/>
-      <c r="E8" s="16"/>
-      <c r="F8" s="16"/>
-      <c r="G8" s="16"/>
-      <c r="H8" s="16"/>
-      <c r="I8" s="17"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="11"/>
+      <c r="H8" s="11"/>
+      <c r="I8" s="12"/>
     </row>
     <row r="9" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="15" t="s">
+      <c r="A9" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="16" t="s">
+      <c r="B9" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="16"/>
-      <c r="D9" s="16"/>
-      <c r="E9" s="16"/>
-      <c r="F9" s="16"/>
-      <c r="G9" s="16"/>
-      <c r="H9" s="16"/>
-      <c r="I9" s="17"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="11"/>
+      <c r="I9" s="12"/>
     </row>
     <row r="10" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="15" t="s">
+      <c r="A10" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="B10" s="16" t="s">
+      <c r="B10" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="16" t="s">
+      <c r="C10" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="D10" s="16"/>
-      <c r="E10" s="16" t="s">
+      <c r="D10" s="11"/>
+      <c r="E10" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="F10" s="16" t="s">
+      <c r="F10" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="G10" s="16" t="s">
+      <c r="G10" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="H10" s="16"/>
-      <c r="I10" s="17"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="12"/>
     </row>
     <row r="11" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="15" t="s">
+      <c r="A11" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="B11" s="16" t="s">
+      <c r="B11" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="C11" s="16"/>
-      <c r="D11" s="16" t="s">
+      <c r="C11" s="11"/>
+      <c r="D11" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="E11" s="16"/>
-      <c r="F11" s="16"/>
-      <c r="G11" s="16"/>
-      <c r="H11" s="16"/>
-      <c r="I11" s="17"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="11"/>
+      <c r="I11" s="12"/>
     </row>
     <row r="12" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="15" t="s">
+      <c r="A12" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="B12" s="16" t="s">
+      <c r="B12" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="C12" s="16" t="s">
+      <c r="C12" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="D12" s="16"/>
-      <c r="E12" s="16"/>
-      <c r="F12" s="16"/>
-      <c r="G12" s="16"/>
-      <c r="H12" s="16"/>
-      <c r="I12" s="17"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
+      <c r="H12" s="11"/>
+      <c r="I12" s="12"/>
     </row>
     <row r="13" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="15" t="s">
+      <c r="A13" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="B13" s="16" t="s">
+      <c r="B13" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="C13" s="16" t="s">
+      <c r="C13" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="16"/>
-      <c r="G13" s="16"/>
-      <c r="H13" s="16"/>
-      <c r="I13" s="17"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="12"/>
     </row>
     <row r="14" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="15" t="s">
+      <c r="A14" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="B14" s="16" t="s">
+      <c r="B14" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="16"/>
-      <c r="D14" s="16"/>
-      <c r="E14" s="16"/>
-      <c r="F14" s="16"/>
-      <c r="G14" s="16"/>
-      <c r="H14" s="16"/>
-      <c r="I14" s="17"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="11"/>
+      <c r="I14" s="12"/>
     </row>
     <row r="15" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="15" t="s">
+      <c r="A15" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="B15" s="16" t="s">
+      <c r="B15" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="C15" s="16"/>
-      <c r="D15" s="16"/>
-      <c r="E15" s="16" t="s">
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="F15" s="16" t="s">
+      <c r="F15" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="G15" s="16"/>
-      <c r="H15" s="16"/>
-      <c r="I15" s="17"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="11"/>
+      <c r="I15" s="12"/>
     </row>
     <row r="16" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="15" t="s">
+      <c r="A16" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="16" t="s">
+      <c r="B16" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="C16" s="16" t="s">
+      <c r="C16" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="D16" s="16" t="s">
+      <c r="D16" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="E16" s="16"/>
-      <c r="F16" s="16"/>
-      <c r="G16" s="16"/>
-      <c r="H16" s="16"/>
-      <c r="I16" s="17" t="s">
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="11"/>
+      <c r="H16" s="11"/>
+      <c r="I16" s="12" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="15" t="s">
+      <c r="A17" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="B17" s="16" t="s">
+      <c r="B17" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="C17" s="16" t="s">
+      <c r="C17" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="D17" s="16"/>
-      <c r="E17" s="16"/>
-      <c r="F17" s="16"/>
-      <c r="G17" s="16"/>
-      <c r="H17" s="16"/>
-      <c r="I17" s="17"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="11"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="11"/>
+      <c r="H17" s="11"/>
+      <c r="I17" s="12"/>
     </row>
     <row r="18" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="15" t="s">
+      <c r="A18" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="B18" s="16" t="s">
+      <c r="B18" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C18" s="16" t="s">
+      <c r="C18" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="D18" s="16"/>
-      <c r="E18" s="16"/>
-      <c r="F18" s="16"/>
-      <c r="G18" s="16"/>
-      <c r="H18" s="16"/>
-      <c r="I18" s="17"/>
+      <c r="D18" s="11"/>
+      <c r="E18" s="11"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="11"/>
+      <c r="H18" s="11"/>
+      <c r="I18" s="12"/>
     </row>
     <row r="19" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="15" t="s">
+      <c r="A19" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="B19" s="16" t="s">
+      <c r="B19" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="C19" s="16" t="s">
+      <c r="C19" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="D19" s="16" t="s">
+      <c r="D19" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="E19" s="16"/>
-      <c r="F19" s="16"/>
-      <c r="G19" s="16"/>
-      <c r="H19" s="16"/>
-      <c r="I19" s="17"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="11"/>
+      <c r="I19" s="12"/>
     </row>
     <row r="20" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="15" t="s">
+      <c r="A20" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="B20" s="16" t="s">
+      <c r="B20" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="C20" s="16" t="s">
+      <c r="C20" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="D20" s="16" t="s">
+      <c r="D20" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="E20" s="16" t="s">
+      <c r="E20" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="F20" s="16" t="s">
+      <c r="F20" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="G20" s="16" t="s">
+      <c r="G20" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="H20" s="16"/>
-      <c r="I20" s="17"/>
+      <c r="H20" s="11"/>
+      <c r="I20" s="12"/>
     </row>
     <row r="21" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="15" t="s">
+      <c r="A21" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="B21" s="16" t="s">
+      <c r="B21" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="C21" s="16"/>
-      <c r="D21" s="16" t="s">
+      <c r="C21" s="11"/>
+      <c r="D21" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="E21" s="16"/>
-      <c r="F21" s="16"/>
-      <c r="G21" s="16"/>
-      <c r="H21" s="16"/>
-      <c r="I21" s="17"/>
+      <c r="E21" s="11"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="11"/>
+      <c r="H21" s="11"/>
+      <c r="I21" s="12"/>
     </row>
     <row r="22" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="15" t="s">
+      <c r="A22" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="B22" s="16" t="s">
+      <c r="B22" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="C22" s="16" t="s">
+      <c r="C22" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="16" t="s">
+      <c r="D22" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="E22" s="16"/>
-      <c r="F22" s="16"/>
-      <c r="G22" s="16"/>
-      <c r="H22" s="16" t="s">
+      <c r="E22" s="11"/>
+      <c r="F22" s="11"/>
+      <c r="G22" s="11"/>
+      <c r="H22" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="I22" s="17"/>
+      <c r="I22" s="12"/>
     </row>
     <row r="23" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="15" t="s">
+      <c r="A23" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="B23" s="16" t="s">
+      <c r="B23" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="C23" s="16" t="s">
+      <c r="C23" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="D23" s="16" t="s">
+      <c r="D23" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="E23" s="16"/>
-      <c r="F23" s="16"/>
-      <c r="G23" s="16"/>
-      <c r="H23" s="16" t="s">
+      <c r="E23" s="11"/>
+      <c r="F23" s="11"/>
+      <c r="G23" s="11"/>
+      <c r="H23" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="I23" s="17"/>
+      <c r="I23" s="12"/>
     </row>
     <row r="24" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="15" t="s">
+      <c r="A24" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="B24" s="16" t="s">
+      <c r="B24" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="C24" s="16"/>
-      <c r="D24" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="E24" s="16"/>
-      <c r="F24" s="16"/>
-      <c r="G24" s="16"/>
-      <c r="H24" s="16"/>
-      <c r="I24" s="17"/>
+      <c r="C24" s="11"/>
+      <c r="D24" s="13">
+        <v>0.66597222222222219</v>
+      </c>
+      <c r="E24" s="11"/>
+      <c r="F24" s="11"/>
+      <c r="G24" s="11"/>
+      <c r="H24" s="11"/>
+      <c r="I24" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1362,16 +1359,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="B1" s="17"/>
+    </row>
+    <row r="2" spans="1:2" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="B1" s="9"/>
-    </row>
-    <row r="2" spans="1:2" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="B2" s="9"/>
+      <c r="B2" s="17"/>
     </row>
     <row r="3" spans="1:2" ht="8" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
@@ -1379,42 +1376,42 @@
     </row>
     <row r="4" spans="1:2" ht="84" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B4" s="6" t="s">
         <v>68</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B5" s="7" t="s">
         <v>70</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="B6" s="6" t="s">
         <v>72</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="140" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B7" s="7" t="s">
         <v>74</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="126" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="B8" s="6" t="s">
         <v>76</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
@@ -1443,142 +1440,142 @@
   <sheetData>
     <row r="1" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C1" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>80</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>84</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>90</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="C5" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>93</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>96</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="C7" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>99</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="C8" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>102</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="C9" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>105</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="C10" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>108</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>109</v>
       </c>
     </row>
   </sheetData>

--- a/docs/shows/shows.xlsx
+++ b/docs/shows/shows.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/milesshultz/Documents/kings_website/rock/docs/shows/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{25EF77C3-CC6A-0244-B57E-1E573E19DF43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D02D081D-8BDD-5A4F-B921-0AF4DEB9AD3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="110">
   <si>
     <t>HOW TO ADD A SHOW: Fill in a new row below. Date format: YYYY-MM-DD. Cancelled: TRUE or FALSE. Leave optional columns blank if not needed. After saving, run:  python scripts/update_shows.py  then commit &amp; push.</t>
   </si>
@@ -376,6 +376,9 @@
   </si>
   <si>
     <t>Enter TRUE to mark show as cancelled; leave blank otherwise</t>
+  </si>
+  <si>
+    <t>4:00 PM</t>
   </si>
 </sst>
 </file>
@@ -571,9 +574,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="20" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -584,6 +584,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="4" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -904,17 +907,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
     </row>
     <row r="2" spans="1:9" ht="54" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
@@ -1332,8 +1335,8 @@
         <v>11</v>
       </c>
       <c r="C24" s="11"/>
-      <c r="D24" s="13">
-        <v>0.66597222222222219</v>
+      <c r="D24" s="18" t="s">
+        <v>109</v>
       </c>
       <c r="E24" s="11"/>
       <c r="F24" s="11"/>
@@ -1359,16 +1362,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="B1" s="17"/>
+      <c r="B1" s="16"/>
     </row>
     <row r="2" spans="1:2" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="B2" s="17"/>
+      <c r="B2" s="16"/>
     </row>
     <row r="3" spans="1:2" ht="8" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>

--- a/docs/shows/shows.xlsx
+++ b/docs/shows/shows.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/milesshultz/Documents/kings_website/rock/docs/shows/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8B138E72-B7A8-954E-B2B2-6FDB1EAE6C18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DA3B93A6-FF29-DE44-9B55-AC4596DA08FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -582,7 +582,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -629,6 +629,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="18" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1352,7 +1355,9 @@
       <c r="D22" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="E22" s="11"/>
+      <c r="E22" s="19">
+        <v>0.75</v>
+      </c>
       <c r="F22" s="11" t="s">
         <v>61</v>
       </c>
@@ -1376,7 +1381,9 @@
       <c r="D23" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="E23" s="11"/>
+      <c r="E23" s="19">
+        <v>0.83333333333333337</v>
+      </c>
       <c r="F23" s="11"/>
       <c r="G23" s="11"/>
       <c r="H23" s="11"/>

--- a/docs/shows/shows.xlsx
+++ b/docs/shows/shows.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/milesshultz/Documents/kings_website/rock/docs/shows/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DA3B93A6-FF29-DE44-9B55-AC4596DA08FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{628D43E2-DCE5-4145-8E99-16E66A399AE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,9 +22,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="123">
-  <si>
-    <t>HOW TO ADD A SHOW: Fill in a new row below. Date format: YYYY-MM-DD. Start/End Time format: H:MM AM/PM (e.g. 7:00 PM). Cancelled: TRUE or FALSE. Leave optional columns blank if not needed. After saving, run:  python docs/shows/update_shows.py  then commit &amp; push.</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="129">
+  <si>
+    <t>HOW TO ADD A SHOW: Fill in a new row below. Date format: YYYY-MM-DD. Start/End Time: H:MM AM/PM (e.g. 7:00 PM). Address: full street address for Maps link (e.g. 1600 Dodge Ave, Evanston, IL 60201). Cancelled: TRUE or FALSE. Leave optional columns blank if not needed. After saving, run:  python docs/shows/update_shows.py  then commit &amp; push.</t>
   </si>
   <si>
     <t>Date
@@ -47,6 +47,10 @@
   </si>
   <si>
     <t>Location
+(optional)</t>
+  </si>
+  <si>
+    <t>Address
 (optional)</t>
   </si>
   <si>
@@ -366,28 +370,37 @@
     <t>Location</t>
   </si>
   <si>
-    <t>Neighborhood or sub-location, e.g. "ETHS Lazier Field"</t>
+    <t>Sub-location within the venue, e.g. "ETHS Lazier Field"</t>
   </si>
   <si>
     <t>G</t>
   </si>
   <si>
+    <t>Address</t>
+  </si>
+  <si>
+    <t>Full street address for Google Maps link, e.g. "1600 Dodge Ave, Evanston, IL 60201"</t>
+  </si>
+  <si>
+    <t>H</t>
+  </si>
+  <si>
     <t>Detail</t>
   </si>
   <si>
     <t>Event sub-title, e.g. "PTA Spring Fling". Not for time/location.</t>
   </si>
   <si>
-    <t>H</t>
+    <t>I</t>
   </si>
   <si>
     <t>Detail Link Name</t>
   </si>
   <si>
-    <t>Linked text shown after the detail, e.g. "Covenant Nursery School"</t>
-  </si>
-  <si>
-    <t>I</t>
+    <t>Linked text shown after the detail</t>
+  </si>
+  <si>
+    <t>J</t>
   </si>
   <si>
     <t>Detail Link URL</t>
@@ -396,7 +409,7 @@
     <t>URL for the detail link</t>
   </si>
   <si>
-    <t>J</t>
+    <t>K</t>
   </si>
   <si>
     <t>Detail Link Suffix</t>
@@ -405,29 +418,35 @@
     <t>Plain text after the link, e.g. "Dining for Dollars"</t>
   </si>
   <si>
-    <t>K</t>
+    <t>L</t>
   </si>
   <si>
     <t>Description</t>
   </si>
   <si>
-    <t>Italic blurb shown below the venue name</t>
-  </si>
-  <si>
-    <t>L</t>
+    <t>Italic blurb shown below the show info</t>
+  </si>
+  <si>
+    <t>M</t>
   </si>
   <si>
     <t>Cancelled</t>
   </si>
   <si>
     <t>TRUE if the show was cancelled; leave blank otherwise</t>
+  </si>
+  <si>
+    <t>2285 Church St, Evanston, IL 60201</t>
+  </si>
+  <si>
+    <t>908 Seward St, Evanston, IL 60202</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -494,6 +513,12 @@
       <color rgb="FFE8DFC0"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Courier New"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="8">
@@ -582,7 +607,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -619,6 +644,9 @@
     <xf numFmtId="20" fontId="4" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="18" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -630,9 +658,7 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="18" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -935,7 +961,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L24"/>
+  <dimension ref="A1:M24"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18" style="8" customWidth="1"/>
@@ -947,24 +973,24 @@
     <col min="7" max="7" width="23.6640625" style="8" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="129.6640625" style="8" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="15.1640625" style="8" bestFit="1" customWidth="1"/>
-    <col min="10" max="12" width="8.83203125" style="8" customWidth="1"/>
-    <col min="13" max="16384" width="8.83203125" style="8"/>
+    <col min="10" max="13" width="8.83203125" style="8" customWidth="1"/>
+    <col min="14" max="16384" width="8.83203125" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
+    <row r="1" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
-    </row>
-    <row r="2" spans="1:12" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+    </row>
+    <row r="2" spans="1:13" ht="54" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
         <v>1</v>
       </c>
@@ -1001,13 +1027,16 @@
       <c r="L2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="3" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" s="11"/>
       <c r="D3" s="11"/>
@@ -1017,32 +1046,32 @@
       <c r="H3" s="11"/>
       <c r="I3" s="12"/>
     </row>
-    <row r="4" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C4" s="11"/>
       <c r="D4" s="11"/>
       <c r="E4" s="11"/>
       <c r="F4" s="11"/>
-      <c r="G4" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="H4" s="11"/>
+      <c r="G4" s="11"/>
+      <c r="H4" s="11" t="s">
+        <v>18</v>
+      </c>
       <c r="I4" s="12"/>
     </row>
-    <row r="5" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D5" s="11"/>
       <c r="E5" s="11"/>
@@ -1051,15 +1080,15 @@
       <c r="H5" s="11"/>
       <c r="I5" s="12"/>
     </row>
-    <row r="6" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D6" s="11"/>
       <c r="E6" s="11"/>
@@ -1068,12 +1097,12 @@
       <c r="H6" s="11"/>
       <c r="I6" s="12"/>
     </row>
-    <row r="7" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C7" s="11"/>
       <c r="D7" s="11"/>
@@ -1083,15 +1112,15 @@
       <c r="H7" s="11"/>
       <c r="I7" s="12"/>
     </row>
-    <row r="8" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D8" s="11"/>
       <c r="E8" s="11"/>
@@ -1100,12 +1129,12 @@
       <c r="H8" s="11"/>
       <c r="I8" s="12"/>
     </row>
-    <row r="9" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C9" s="11"/>
       <c r="D9" s="11"/>
@@ -1115,56 +1144,57 @@
       <c r="H9" s="11"/>
       <c r="I9" s="12"/>
     </row>
-    <row r="10" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D10" s="11"/>
       <c r="E10" s="11"/>
       <c r="F10" s="11"/>
       <c r="G10" s="11"/>
-      <c r="H10" s="11" t="s">
-        <v>29</v>
-      </c>
+      <c r="H10" s="11"/>
       <c r="I10" s="12" t="s">
         <v>30</v>
       </c>
       <c r="J10" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="11" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C11" s="11"/>
       <c r="D11" s="11"/>
       <c r="E11" s="11"/>
       <c r="F11" s="11"/>
-      <c r="G11" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="H11" s="11"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="11" t="s">
+        <v>18</v>
+      </c>
       <c r="I11" s="12"/>
     </row>
-    <row r="12" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D12" s="11"/>
       <c r="E12" s="11"/>
@@ -1173,15 +1203,15 @@
       <c r="H12" s="11"/>
       <c r="I12" s="12"/>
     </row>
-    <row r="13" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D13" s="11"/>
       <c r="E13" s="11"/>
@@ -1190,12 +1220,12 @@
       <c r="H13" s="11"/>
       <c r="I13" s="12"/>
     </row>
-    <row r="14" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C14" s="11"/>
       <c r="D14" s="11"/>
@@ -1205,56 +1235,57 @@
       <c r="H14" s="11"/>
       <c r="I14" s="12"/>
     </row>
-    <row r="15" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C15" s="11"/>
       <c r="D15" s="11"/>
       <c r="E15" s="11"/>
       <c r="F15" s="11"/>
       <c r="G15" s="11"/>
-      <c r="H15" s="11" t="s">
-        <v>40</v>
-      </c>
+      <c r="H15" s="11"/>
       <c r="I15" s="12" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="16" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J15" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D16" s="11"/>
       <c r="E16" s="11"/>
       <c r="F16" s="11"/>
-      <c r="G16" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="H16" s="11"/>
+      <c r="G16" s="11"/>
+      <c r="H16" s="11" t="s">
+        <v>46</v>
+      </c>
       <c r="I16" s="12"/>
-      <c r="L16" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M16" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D17" s="11"/>
       <c r="E17" s="11"/>
@@ -1263,15 +1294,15 @@
       <c r="H17" s="11"/>
       <c r="I17" s="12"/>
     </row>
-    <row r="18" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D18" s="11"/>
       <c r="E18" s="11"/>
@@ -1280,61 +1311,62 @@
       <c r="H18" s="11"/>
       <c r="I18" s="12"/>
     </row>
-    <row r="19" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D19" s="11"/>
       <c r="E19" s="11"/>
       <c r="F19" s="11"/>
-      <c r="G19" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="H19" s="11"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="11" t="s">
+        <v>55</v>
+      </c>
       <c r="I19" s="12"/>
     </row>
-    <row r="20" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E20" s="11"/>
       <c r="F20" s="11"/>
       <c r="G20" s="11"/>
-      <c r="H20" s="11" t="s">
-        <v>29</v>
-      </c>
+      <c r="H20" s="11"/>
       <c r="I20" s="12" t="s">
         <v>30</v>
       </c>
       <c r="J20" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="21" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="K20" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C21" s="11"/>
       <c r="D21" s="11" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E21" s="11"/>
       <c r="F21" s="11"/>
@@ -1342,70 +1374,73 @@
       <c r="H21" s="11"/>
       <c r="I21" s="12"/>
     </row>
-    <row r="22" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="E22" s="19">
+        <v>61</v>
+      </c>
+      <c r="E22" s="14">
         <v>0.75</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="G22" s="11"/>
+        <v>62</v>
+      </c>
+      <c r="G22" s="20" t="s">
+        <v>127</v>
+      </c>
       <c r="H22" s="11"/>
       <c r="I22" s="12"/>
-      <c r="K22" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L22" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="E23" s="19">
+        <v>67</v>
+      </c>
+      <c r="E23" s="14">
         <v>0.83333333333333337</v>
       </c>
       <c r="F23" s="11"/>
-      <c r="G23" s="11"/>
+      <c r="G23" s="20" t="s">
+        <v>128</v>
+      </c>
       <c r="H23" s="11"/>
       <c r="I23" s="12"/>
-      <c r="K23" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L23" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C24" s="11"/>
       <c r="D24" s="13" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E24" s="11"/>
       <c r="F24" s="11"/>
-      <c r="G24" s="11"/>
       <c r="H24" s="11"/>
       <c r="I24" s="12"/>
     </row>
@@ -1427,16 +1462,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="18" t="s">
-        <v>70</v>
-      </c>
-      <c r="B1" s="17"/>
+      <c r="A1" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="B1" s="18"/>
     </row>
     <row r="2" spans="1:2" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="16" t="s">
-        <v>71</v>
-      </c>
-      <c r="B2" s="17"/>
+      <c r="A2" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="B2" s="18"/>
     </row>
     <row r="3" spans="1:2" ht="8" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
@@ -1444,42 +1479,42 @@
     </row>
     <row r="4" spans="1:2" ht="84" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="140" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="126" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
@@ -1497,7 +1532,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1508,184 +1543,198 @@
   <sheetData>
     <row r="1" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B11" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C11" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D11" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B12" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C12" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D12" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B13" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C13" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D13" t="s">
-        <v>122</v>
+        <v>123</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>124</v>
+      </c>
+      <c r="B14" t="s">
+        <v>125</v>
+      </c>
+      <c r="C14" t="s">
+        <v>95</v>
+      </c>
+      <c r="D14" t="s">
+        <v>126</v>
       </c>
     </row>
   </sheetData>

--- a/docs/shows/shows.xlsx
+++ b/docs/shows/shows.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/milesshultz/Documents/kings_website/rock/docs/shows/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{628D43E2-DCE5-4145-8E99-16E66A399AE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3094875D-9FB7-0442-B391-094CF6DA0F44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -225,9 +225,6 @@
     <t>ETHS Lazier Field</t>
   </si>
   <si>
-    <t>Pre-game set before the Chicago Union — a pro Ultimate Frisbee Association (UFA) team — takes the field.</t>
-  </si>
-  <si>
     <t>2026-06-24</t>
   </si>
   <si>
@@ -440,6 +437,9 @@
   </si>
   <si>
     <t>908 Seward St, Evanston, IL 60202</t>
+  </si>
+  <si>
+    <t>Pre-game set before the Chicago Union (our pro Ultimate Frisbee Association (UFA) team) takes the field!</t>
   </si>
 </sst>
 </file>
@@ -647,6 +647,7 @@
     <xf numFmtId="18" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -658,7 +659,6 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -978,17 +978,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
     </row>
     <row r="2" spans="1:13" ht="54" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
@@ -1393,51 +1393,51 @@
       <c r="F22" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="G22" s="20" t="s">
-        <v>127</v>
+      <c r="G22" s="15" t="s">
+        <v>126</v>
       </c>
       <c r="H22" s="11"/>
       <c r="I22" s="12"/>
       <c r="L22" t="s">
-        <v>63</v>
+        <v>128</v>
       </c>
     </row>
     <row r="23" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="B23" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="B23" s="11" t="s">
+      <c r="C23" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="C23" s="11" t="s">
+      <c r="D23" s="11" t="s">
         <v>66</v>
-      </c>
-      <c r="D23" s="11" t="s">
-        <v>67</v>
       </c>
       <c r="E23" s="14">
         <v>0.83333333333333337</v>
       </c>
       <c r="F23" s="11"/>
-      <c r="G23" s="20" t="s">
-        <v>128</v>
+      <c r="G23" s="15" t="s">
+        <v>127</v>
       </c>
       <c r="H23" s="11"/>
       <c r="I23" s="12"/>
       <c r="L23" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="24" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B24" s="11" t="s">
         <v>15</v>
       </c>
       <c r="C24" s="11"/>
       <c r="D24" s="13" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E24" s="11"/>
       <c r="F24" s="11"/>
@@ -1462,16 +1462,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="B1" s="19"/>
+    </row>
+    <row r="2" spans="1:2" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="B1" s="18"/>
-    </row>
-    <row r="2" spans="1:2" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="B2" s="18"/>
+      <c r="B2" s="19"/>
     </row>
     <row r="3" spans="1:2" ht="8" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
@@ -1479,42 +1479,42 @@
     </row>
     <row r="4" spans="1:2" ht="84" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="B4" s="6" t="s">
         <v>73</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="B5" s="7" t="s">
         <v>75</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B6" s="6" t="s">
         <v>77</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="140" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B7" s="7" t="s">
         <v>79</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="126" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B8" s="6" t="s">
         <v>81</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
@@ -1543,198 +1543,198 @@
   <sheetData>
     <row r="1" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C1" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>85</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>89</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>95</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="C5" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>98</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>101</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="C7" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>104</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="C8" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>107</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="C9" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>110</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="C10" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>113</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
+        <v>114</v>
+      </c>
+      <c r="B11" t="s">
         <v>115</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
+        <v>94</v>
+      </c>
+      <c r="D11" t="s">
         <v>116</v>
-      </c>
-      <c r="C11" t="s">
-        <v>95</v>
-      </c>
-      <c r="D11" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
+        <v>117</v>
+      </c>
+      <c r="B12" t="s">
         <v>118</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
+        <v>94</v>
+      </c>
+      <c r="D12" t="s">
         <v>119</v>
-      </c>
-      <c r="C12" t="s">
-        <v>95</v>
-      </c>
-      <c r="D12" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
+        <v>120</v>
+      </c>
+      <c r="B13" t="s">
         <v>121</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
+        <v>94</v>
+      </c>
+      <c r="D13" t="s">
         <v>122</v>
-      </c>
-      <c r="C13" t="s">
-        <v>95</v>
-      </c>
-      <c r="D13" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
+        <v>123</v>
+      </c>
+      <c r="B14" t="s">
         <v>124</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
+        <v>94</v>
+      </c>
+      <c r="D14" t="s">
         <v>125</v>
-      </c>
-      <c r="C14" t="s">
-        <v>95</v>
-      </c>
-      <c r="D14" t="s">
-        <v>126</v>
       </c>
     </row>
   </sheetData>

--- a/docs/shows/shows.xlsx
+++ b/docs/shows/shows.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/milesshultz/Documents/kings_website/rock/docs/shows/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3094875D-9FB7-0442-B391-094CF6DA0F44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F69A4548-208C-7B46-8450-AC297BF2D94B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -439,7 +439,7 @@
     <t>908 Seward St, Evanston, IL 60202</t>
   </si>
   <si>
-    <t>Pre-game set before the Chicago Union (our pro Ultimate Frisbee Association (UFA) team) takes the field!</t>
+    <t>Pre-game set before the Chicago Union (our pro Ultimate Frisbee Association team) takes the field!</t>
   </si>
 </sst>
 </file>

--- a/docs/shows/shows.xlsx
+++ b/docs/shows/shows.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/milesshultz/Documents/kings_website/rock/docs/shows/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F69A4548-208C-7B46-8450-AC297BF2D94B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E2AB649-4376-E340-9C76-7F509F54A158}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="137">
   <si>
     <t>HOW TO ADD A SHOW: Fill in a new row below. Date format: YYYY-MM-DD. Start/End Time: H:MM AM/PM (e.g. 7:00 PM). Address: full street address for Maps link (e.g. 1600 Dodge Ave, Evanston, IL 60201). Cancelled: TRUE or FALSE. Leave optional columns blank if not needed. After saving, run:  python docs/shows/update_shows.py  then commit &amp; push.</t>
   </si>
@@ -441,12 +441,36 @@
   <si>
     <t>Pre-game set before the Chicago Union (our pro Ultimate Frisbee Association team) takes the field!</t>
   </si>
+  <si>
+    <t>2902 Central St, Evanston, IL 60201</t>
+  </si>
+  <si>
+    <t>2600 Colfax St, Evanston, IL 60201</t>
+  </si>
+  <si>
+    <t>2311 N Campus Dr, Evanston, IL 60201</t>
+  </si>
+  <si>
+    <t>1030 Central St, Evanston, IL 60201</t>
+  </si>
+  <si>
+    <t>Ackerman Park, Evanston, IL 60201</t>
+  </si>
+  <si>
+    <t>2948 Central St, Evanston, IL 60201</t>
+  </si>
+  <si>
+    <t>2121 Ashland Ave, Evanston, IL 60201</t>
+  </si>
+  <si>
+    <t>4701 N Cumberland Ave Suite 33, Norridge, IL 60706</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -519,6 +543,18 @@
       <color rgb="FF1F1F1F"/>
       <name val="Courier New"/>
       <family val="1"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="8">
@@ -607,7 +643,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -659,6 +695,8 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -970,7 +1008,7 @@
     <col min="4" max="4" width="35.6640625" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="37" style="8" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="46.5" style="8" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="23.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="43" style="8" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="129.6640625" style="8" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="15.1640625" style="8" bestFit="1" customWidth="1"/>
     <col min="10" max="13" width="8.83203125" style="8" customWidth="1"/>
@@ -1039,8 +1077,12 @@
         <v>15</v>
       </c>
       <c r="C3" s="11"/>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11"/>
+      <c r="D3" s="14">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="E3" s="14">
+        <v>0.75</v>
+      </c>
       <c r="F3" s="11"/>
       <c r="G3" s="11"/>
       <c r="H3" s="11"/>
@@ -1054,10 +1096,16 @@
         <v>17</v>
       </c>
       <c r="C4" s="11"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
+      <c r="D4" s="14">
+        <v>0.5</v>
+      </c>
+      <c r="E4" s="14">
+        <v>0.5625</v>
+      </c>
       <c r="F4" s="11"/>
-      <c r="G4" s="11"/>
+      <c r="G4" s="21" t="s">
+        <v>130</v>
+      </c>
       <c r="H4" s="11" t="s">
         <v>18</v>
       </c>
@@ -1076,7 +1124,9 @@
       <c r="D5" s="11"/>
       <c r="E5" s="11"/>
       <c r="F5" s="11"/>
-      <c r="G5" s="11"/>
+      <c r="G5" s="21" t="s">
+        <v>129</v>
+      </c>
       <c r="H5" s="11"/>
       <c r="I5" s="12"/>
     </row>
@@ -1093,7 +1143,9 @@
       <c r="D6" s="11"/>
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
-      <c r="G6" s="11"/>
+      <c r="G6" s="22" t="s">
+        <v>131</v>
+      </c>
       <c r="H6" s="11"/>
       <c r="I6" s="12"/>
     </row>
@@ -1108,7 +1160,6 @@
       <c r="D7" s="11"/>
       <c r="E7" s="11"/>
       <c r="F7" s="11"/>
-      <c r="G7" s="11"/>
       <c r="H7" s="11"/>
       <c r="I7" s="12"/>
     </row>
@@ -1125,7 +1176,9 @@
       <c r="D8" s="11"/>
       <c r="E8" s="11"/>
       <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
+      <c r="G8" s="21" t="s">
+        <v>129</v>
+      </c>
       <c r="H8" s="11"/>
       <c r="I8" s="12"/>
     </row>
@@ -1137,8 +1190,12 @@
         <v>15</v>
       </c>
       <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
+      <c r="D9" s="14">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="E9" s="14">
+        <v>0.75</v>
+      </c>
       <c r="F9" s="11"/>
       <c r="G9" s="11"/>
       <c r="H9" s="11"/>
@@ -1157,7 +1214,9 @@
       <c r="D10" s="11"/>
       <c r="E10" s="11"/>
       <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
+      <c r="G10" s="21" t="s">
+        <v>129</v>
+      </c>
       <c r="H10" s="11"/>
       <c r="I10" s="12" t="s">
         <v>30</v>
@@ -1177,10 +1236,16 @@
         <v>17</v>
       </c>
       <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
+      <c r="D11" s="14">
+        <v>0.5</v>
+      </c>
+      <c r="E11" s="14">
+        <v>0.5625</v>
+      </c>
       <c r="F11" s="11"/>
-      <c r="G11" s="11"/>
+      <c r="G11" s="21" t="s">
+        <v>130</v>
+      </c>
       <c r="H11" s="11" t="s">
         <v>18</v>
       </c>
@@ -1199,7 +1264,9 @@
       <c r="D12" s="11"/>
       <c r="E12" s="11"/>
       <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
+      <c r="G12" s="21" t="s">
+        <v>129</v>
+      </c>
       <c r="H12" s="11"/>
       <c r="I12" s="12"/>
     </row>
@@ -1216,7 +1283,9 @@
       <c r="D13" s="11"/>
       <c r="E13" s="11"/>
       <c r="F13" s="11"/>
-      <c r="G13" s="11"/>
+      <c r="G13" s="11" t="s">
+        <v>132</v>
+      </c>
       <c r="H13" s="11"/>
       <c r="I13" s="12"/>
     </row>
@@ -1246,7 +1315,9 @@
       <c r="D15" s="11"/>
       <c r="E15" s="11"/>
       <c r="F15" s="11"/>
-      <c r="G15" s="11"/>
+      <c r="G15" s="11" t="s">
+        <v>133</v>
+      </c>
       <c r="H15" s="11"/>
       <c r="I15" s="12" t="s">
         <v>41</v>
@@ -1268,7 +1339,9 @@
       <c r="D16" s="11"/>
       <c r="E16" s="11"/>
       <c r="F16" s="11"/>
-      <c r="G16" s="11"/>
+      <c r="G16" s="21" t="s">
+        <v>134</v>
+      </c>
       <c r="H16" s="11" t="s">
         <v>46</v>
       </c>
@@ -1287,10 +1360,16 @@
       <c r="C17" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="D17" s="11"/>
-      <c r="E17" s="11"/>
+      <c r="D17" s="14">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="E17" s="14">
+        <v>0.83333333333333337</v>
+      </c>
       <c r="F17" s="11"/>
-      <c r="G17" s="11"/>
+      <c r="G17" s="21" t="s">
+        <v>135</v>
+      </c>
       <c r="H17" s="11"/>
       <c r="I17" s="12"/>
     </row>
@@ -1304,10 +1383,16 @@
       <c r="C18" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="D18" s="11"/>
-      <c r="E18" s="11"/>
+      <c r="D18" s="14">
+        <v>0.875</v>
+      </c>
+      <c r="E18" s="14">
+        <v>0.5</v>
+      </c>
       <c r="F18" s="11"/>
-      <c r="G18" s="11"/>
+      <c r="G18" s="21" t="s">
+        <v>136</v>
+      </c>
       <c r="H18" s="11"/>
       <c r="I18" s="12"/>
     </row>
@@ -1321,10 +1406,16 @@
       <c r="C19" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="D19" s="11"/>
-      <c r="E19" s="11"/>
+      <c r="D19" s="14">
+        <v>0.8125</v>
+      </c>
+      <c r="E19" s="14">
+        <v>0.86458333333333337</v>
+      </c>
       <c r="F19" s="11"/>
-      <c r="G19" s="11"/>
+      <c r="G19" s="11" t="s">
+        <v>132</v>
+      </c>
       <c r="H19" s="11" t="s">
         <v>55</v>
       </c>
@@ -1343,9 +1434,13 @@
       <c r="D20" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="E20" s="11"/>
+      <c r="E20" s="14">
+        <v>0.79166666666666663</v>
+      </c>
       <c r="F20" s="11"/>
-      <c r="G20" s="11"/>
+      <c r="G20" s="21" t="s">
+        <v>129</v>
+      </c>
       <c r="H20" s="11"/>
       <c r="I20" s="12" t="s">
         <v>30</v>
@@ -1439,7 +1534,9 @@
       <c r="D24" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="E24" s="11"/>
+      <c r="E24" s="14">
+        <v>0.75</v>
+      </c>
       <c r="F24" s="11"/>
       <c r="H24" s="11"/>
       <c r="I24" s="12"/>

--- a/docs/shows/shows.xlsx
+++ b/docs/shows/shows.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/milesshultz/Documents/kings_website/rock/docs/shows/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E2AB649-4376-E340-9C76-7F509F54A158}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBB1C507-A2C9-804F-9CC9-6BE9D2C67557}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="139">
   <si>
     <t>HOW TO ADD A SHOW: Fill in a new row below. Date format: YYYY-MM-DD. Start/End Time: H:MM AM/PM (e.g. 7:00 PM). Address: full street address for Maps link (e.g. 1600 Dodge Ave, Evanston, IL 60201). Cancelled: TRUE or FALSE. Leave optional columns blank if not needed. After saving, run:  python docs/shows/update_shows.py  then commit &amp; push.</t>
   </si>
@@ -464,6 +464,12 @@
   </si>
   <si>
     <t>4701 N Cumberland Ave Suite 33, Norridge, IL 60706</t>
+  </si>
+  <si>
+    <t>Ewing Ave &amp; Payne St, Evanston, IL 60201</t>
+  </si>
+  <si>
+    <t>The greatest block party on our street!</t>
   </si>
 </sst>
 </file>
@@ -684,6 +690,8 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -695,8 +703,6 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1016,17 +1022,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
     </row>
     <row r="2" spans="1:13" ht="54" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
@@ -1084,8 +1090,12 @@
         <v>0.75</v>
       </c>
       <c r="F3" s="11"/>
-      <c r="G3" s="11"/>
-      <c r="H3" s="11"/>
+      <c r="G3" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="H3" s="11" t="s">
+        <v>138</v>
+      </c>
       <c r="I3" s="12"/>
     </row>
     <row r="4" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
@@ -1103,7 +1113,7 @@
         <v>0.5625</v>
       </c>
       <c r="F4" s="11"/>
-      <c r="G4" s="21" t="s">
+      <c r="G4" s="16" t="s">
         <v>130</v>
       </c>
       <c r="H4" s="11" t="s">
@@ -1124,7 +1134,7 @@
       <c r="D5" s="11"/>
       <c r="E5" s="11"/>
       <c r="F5" s="11"/>
-      <c r="G5" s="21" t="s">
+      <c r="G5" s="16" t="s">
         <v>129</v>
       </c>
       <c r="H5" s="11"/>
@@ -1143,7 +1153,7 @@
       <c r="D6" s="11"/>
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
-      <c r="G6" s="22" t="s">
+      <c r="G6" s="17" t="s">
         <v>131</v>
       </c>
       <c r="H6" s="11"/>
@@ -1176,7 +1186,7 @@
       <c r="D8" s="11"/>
       <c r="E8" s="11"/>
       <c r="F8" s="11"/>
-      <c r="G8" s="21" t="s">
+      <c r="G8" s="16" t="s">
         <v>129</v>
       </c>
       <c r="H8" s="11"/>
@@ -1197,8 +1207,12 @@
         <v>0.75</v>
       </c>
       <c r="F9" s="11"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
+      <c r="G9" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="H9" s="11" t="s">
+        <v>138</v>
+      </c>
       <c r="I9" s="12"/>
     </row>
     <row r="10" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
@@ -1214,7 +1228,7 @@
       <c r="D10" s="11"/>
       <c r="E10" s="11"/>
       <c r="F10" s="11"/>
-      <c r="G10" s="21" t="s">
+      <c r="G10" s="16" t="s">
         <v>129</v>
       </c>
       <c r="H10" s="11"/>
@@ -1243,7 +1257,7 @@
         <v>0.5625</v>
       </c>
       <c r="F11" s="11"/>
-      <c r="G11" s="21" t="s">
+      <c r="G11" s="16" t="s">
         <v>130</v>
       </c>
       <c r="H11" s="11" t="s">
@@ -1264,7 +1278,7 @@
       <c r="D12" s="11"/>
       <c r="E12" s="11"/>
       <c r="F12" s="11"/>
-      <c r="G12" s="21" t="s">
+      <c r="G12" s="16" t="s">
         <v>129</v>
       </c>
       <c r="H12" s="11"/>
@@ -1300,8 +1314,12 @@
       <c r="D14" s="11"/>
       <c r="E14" s="11"/>
       <c r="F14" s="11"/>
-      <c r="G14" s="11"/>
-      <c r="H14" s="11"/>
+      <c r="G14" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="H14" s="11" t="s">
+        <v>138</v>
+      </c>
       <c r="I14" s="12"/>
     </row>
     <row r="15" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
@@ -1339,7 +1357,7 @@
       <c r="D16" s="11"/>
       <c r="E16" s="11"/>
       <c r="F16" s="11"/>
-      <c r="G16" s="21" t="s">
+      <c r="G16" s="16" t="s">
         <v>134</v>
       </c>
       <c r="H16" s="11" t="s">
@@ -1367,7 +1385,7 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="F17" s="11"/>
-      <c r="G17" s="21" t="s">
+      <c r="G17" s="16" t="s">
         <v>135</v>
       </c>
       <c r="H17" s="11"/>
@@ -1390,7 +1408,7 @@
         <v>0.5</v>
       </c>
       <c r="F18" s="11"/>
-      <c r="G18" s="21" t="s">
+      <c r="G18" s="16" t="s">
         <v>136</v>
       </c>
       <c r="H18" s="11"/>
@@ -1438,7 +1456,7 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="F20" s="11"/>
-      <c r="G20" s="21" t="s">
+      <c r="G20" s="16" t="s">
         <v>129</v>
       </c>
       <c r="H20" s="11"/>
@@ -1538,7 +1556,12 @@
         <v>0.75</v>
       </c>
       <c r="F24" s="11"/>
-      <c r="H24" s="11"/>
+      <c r="G24" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="H24" s="11" t="s">
+        <v>138</v>
+      </c>
       <c r="I24" s="12"/>
     </row>
   </sheetData>
@@ -1559,16 +1582,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="B1" s="19"/>
+      <c r="B1" s="21"/>
     </row>
     <row r="2" spans="1:2" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="20" t="s">
         <v>71</v>
       </c>
-      <c r="B2" s="19"/>
+      <c r="B2" s="21"/>
     </row>
     <row r="3" spans="1:2" ht="8" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>

--- a/docs/shows/shows.xlsx
+++ b/docs/shows/shows.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/milesshultz/Documents/kings_website/rock/docs/shows/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBB1C507-A2C9-804F-9CC9-6BE9D2C67557}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD77A79A-C552-8C43-A856-4194938255F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1016,8 +1016,11 @@
     <col min="6" max="6" width="46.5" style="8" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="43" style="8" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="129.6640625" style="8" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.1640625" style="8" bestFit="1" customWidth="1"/>
-    <col min="10" max="13" width="8.83203125" style="8" customWidth="1"/>
+    <col min="9" max="9" width="37" style="8" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="33.5" style="8" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="21.5" style="8" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="76.1640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.83203125" style="8" customWidth="1"/>
     <col min="14" max="16384" width="8.83203125" style="8"/>
   </cols>
   <sheetData>
@@ -1093,10 +1096,10 @@
       <c r="G3" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="H3" s="11" t="s">
+      <c r="I3" s="12"/>
+      <c r="L3" s="11" t="s">
         <v>138</v>
       </c>
-      <c r="I3" s="12"/>
     </row>
     <row r="4" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
@@ -1210,10 +1213,10 @@
       <c r="G9" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="H9" s="11" t="s">
+      <c r="I9" s="12"/>
+      <c r="L9" s="11" t="s">
         <v>138</v>
       </c>
-      <c r="I9" s="12"/>
     </row>
     <row r="10" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
@@ -1317,10 +1320,11 @@
       <c r="G14" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="H14" s="11" t="s">
+      <c r="H14" s="11"/>
+      <c r="I14" s="12"/>
+      <c r="L14" s="11" t="s">
         <v>138</v>
       </c>
-      <c r="I14" s="12"/>
     </row>
     <row r="15" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
@@ -1559,10 +1563,10 @@
       <c r="G24" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="H24" s="11" t="s">
+      <c r="I24" s="12"/>
+      <c r="L24" s="11" t="s">
         <v>138</v>
       </c>
-      <c r="I24" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/docs/shows/shows.xlsx
+++ b/docs/shows/shows.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/milesshultz/Documents/kings_website/rock/docs/shows/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD77A79A-C552-8C43-A856-4194938255F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B7BB4BC-AC33-3D4A-BFCF-7CA5F0EE9F0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -476,7 +476,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -549,18 +549,6 @@
       <color rgb="FF1F1F1F"/>
       <name val="Courier New"/>
       <family val="1"/>
-    </font>
-    <font>
-      <sz val="14"/>
-      <color rgb="FF1F1F1F"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF1F1F1F"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="8">
@@ -649,7 +637,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -670,18 +658,8 @@
     <xf numFmtId="0" fontId="9" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="20" fontId="4" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -689,19 +667,33 @@
     <xf numFmtId="18" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1008,563 +1000,566 @@
   <dimension ref="A1:M24"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18" style="8" customWidth="1"/>
-    <col min="2" max="2" width="30.83203125" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="104.5" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="35.6640625" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="37" style="8" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="46.5" style="8" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="43" style="8" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="129.6640625" style="8" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="37" style="8" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="33.5" style="8" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="21.5" style="8" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="76.1640625" style="8" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.83203125" style="8" customWidth="1"/>
-    <col min="14" max="16384" width="8.83203125" style="8"/>
+    <col min="1" max="1" width="18" style="16" customWidth="1"/>
+    <col min="2" max="2" width="30.83203125" style="16" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="104.5" style="16" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="35.6640625" style="16" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="37" style="16" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="46.5" style="16" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="43" style="16" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="129.6640625" style="16" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="37" style="16" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="33.5" style="16" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="21.5" style="16" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="118.83203125" style="16" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.83203125" style="16" customWidth="1"/>
+    <col min="14" max="16384" width="8.83203125" style="16"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
     </row>
     <row r="2" spans="1:13" ht="54" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="E2" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="F2" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="G2" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="9" t="s">
+      <c r="H2" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="9" t="s">
+      <c r="I2" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="K2" t="s">
+      <c r="K2" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="L2" t="s">
+      <c r="L2" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="M2" t="s">
+      <c r="M2" s="16" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="11"/>
-      <c r="D3" s="14">
+      <c r="C3" s="8"/>
+      <c r="D3" s="10">
         <v>0.66666666666666663</v>
       </c>
-      <c r="E3" s="14">
+      <c r="E3" s="10">
         <v>0.75</v>
       </c>
-      <c r="F3" s="11"/>
-      <c r="G3" s="8" t="s">
+      <c r="F3" s="8"/>
+      <c r="G3" s="16" t="s">
         <v>137</v>
       </c>
-      <c r="I3" s="12"/>
-      <c r="L3" s="11" t="s">
+      <c r="I3" s="19"/>
+      <c r="L3" s="8" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="11"/>
-      <c r="D4" s="14">
+      <c r="C4" s="8"/>
+      <c r="D4" s="10">
         <v>0.5</v>
       </c>
-      <c r="E4" s="14">
+      <c r="E4" s="10">
         <v>0.5625</v>
       </c>
-      <c r="F4" s="11"/>
-      <c r="G4" s="16" t="s">
+      <c r="F4" s="8"/>
+      <c r="G4" s="20" t="s">
         <v>130</v>
       </c>
-      <c r="H4" s="11" t="s">
+      <c r="H4" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="I4" s="12"/>
+      <c r="I4" s="19"/>
     </row>
     <row r="5" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="11"/>
-      <c r="E5" s="11"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="16" t="s">
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="20" t="s">
         <v>129</v>
       </c>
-      <c r="H5" s="11"/>
-      <c r="I5" s="12"/>
+      <c r="H5" s="8"/>
+      <c r="I5" s="19"/>
     </row>
     <row r="6" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="10" t="s">
+      <c r="A6" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="D6" s="11"/>
-      <c r="E6" s="11"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="17" t="s">
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="20" t="s">
         <v>131</v>
       </c>
-      <c r="H6" s="11"/>
-      <c r="I6" s="12"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="19"/>
     </row>
     <row r="7" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="10" t="s">
+      <c r="A7" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="C7" s="11"/>
-      <c r="D7" s="11"/>
-      <c r="E7" s="11"/>
-      <c r="F7" s="11"/>
-      <c r="H7" s="11"/>
-      <c r="I7" s="12"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="19"/>
     </row>
     <row r="8" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="10" t="s">
+      <c r="A8" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="C8" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="16" t="s">
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="20" t="s">
         <v>129</v>
       </c>
-      <c r="H8" s="11"/>
-      <c r="I8" s="12"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="19"/>
     </row>
     <row r="9" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="10" t="s">
+      <c r="A9" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="11"/>
-      <c r="D9" s="14">
+      <c r="C9" s="8"/>
+      <c r="D9" s="10">
         <v>0.66666666666666663</v>
       </c>
-      <c r="E9" s="14">
+      <c r="E9" s="10">
         <v>0.75</v>
       </c>
-      <c r="F9" s="11"/>
-      <c r="G9" s="8" t="s">
+      <c r="F9" s="8"/>
+      <c r="G9" s="16" t="s">
         <v>137</v>
       </c>
-      <c r="I9" s="12"/>
-      <c r="L9" s="11" t="s">
+      <c r="I9" s="19"/>
+      <c r="L9" s="8" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="10" t="s">
+      <c r="A10" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="B10" s="11" t="s">
+      <c r="B10" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="16" t="s">
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="20" t="s">
         <v>129</v>
       </c>
-      <c r="H10" s="11"/>
-      <c r="I10" s="12" t="s">
+      <c r="H10" s="8"/>
+      <c r="I10" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="J10" t="s">
+      <c r="J10" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="K10" t="s">
+      <c r="K10" s="16" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="10" t="s">
+      <c r="A11" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="B11" s="11" t="s">
+      <c r="B11" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="11"/>
-      <c r="D11" s="14">
+      <c r="C11" s="8"/>
+      <c r="D11" s="10">
         <v>0.5</v>
       </c>
-      <c r="E11" s="14">
+      <c r="E11" s="10">
         <v>0.5625</v>
       </c>
-      <c r="F11" s="11"/>
-      <c r="G11" s="16" t="s">
+      <c r="F11" s="8"/>
+      <c r="G11" s="20" t="s">
         <v>130</v>
       </c>
-      <c r="H11" s="11" t="s">
+      <c r="H11" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="I11" s="12"/>
+      <c r="I11" s="19"/>
     </row>
     <row r="12" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="10" t="s">
+      <c r="A12" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="B12" s="11" t="s">
+      <c r="B12" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="11" t="s">
+      <c r="C12" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="16" t="s">
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="20" t="s">
         <v>129</v>
       </c>
-      <c r="H12" s="11"/>
-      <c r="I12" s="12"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="19"/>
     </row>
     <row r="13" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="10" t="s">
+      <c r="A13" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="B13" s="11" t="s">
+      <c r="B13" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="11" t="s">
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="H13" s="11"/>
-      <c r="I13" s="12"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="19"/>
     </row>
     <row r="14" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="10" t="s">
+      <c r="A14" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="11" t="s">
+      <c r="B14" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="11"/>
-      <c r="D14" s="11"/>
-      <c r="E14" s="11"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="8" t="s">
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="16" t="s">
         <v>137</v>
       </c>
-      <c r="H14" s="11"/>
-      <c r="I14" s="12"/>
-      <c r="L14" s="11" t="s">
+      <c r="H14" s="8"/>
+      <c r="I14" s="19"/>
+      <c r="L14" s="8" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="10" t="s">
+      <c r="A15" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="11" t="s">
+      <c r="B15" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="C15" s="11"/>
-      <c r="D15" s="11"/>
-      <c r="E15" s="11"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="11" t="s">
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="H15" s="11"/>
-      <c r="I15" s="12" t="s">
+      <c r="H15" s="8"/>
+      <c r="I15" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="J15" t="s">
+      <c r="J15" s="16" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="10" t="s">
+      <c r="A16" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="B16" s="11" t="s">
+      <c r="B16" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="C16" s="11" t="s">
+      <c r="C16" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="D16" s="11"/>
-      <c r="E16" s="11"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="16" t="s">
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="20" t="s">
         <v>134</v>
       </c>
-      <c r="H16" s="11" t="s">
+      <c r="H16" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="I16" s="12"/>
-      <c r="M16" t="s">
+      <c r="I16" s="19"/>
+      <c r="M16" s="16" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="17" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="10" t="s">
+    <row r="17" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="B17" s="11" t="s">
+      <c r="B17" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="C17" s="11" t="s">
+      <c r="C17" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="D17" s="14">
+      <c r="D17" s="10">
         <v>0.79166666666666663</v>
       </c>
-      <c r="E17" s="14">
+      <c r="E17" s="10">
         <v>0.83333333333333337</v>
       </c>
-      <c r="F17" s="11"/>
-      <c r="G17" s="16" t="s">
+      <c r="F17" s="8"/>
+      <c r="G17" s="20" t="s">
         <v>135</v>
       </c>
-      <c r="H17" s="11"/>
-      <c r="I17" s="12"/>
-    </row>
-    <row r="18" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="10" t="s">
+      <c r="H17" s="8"/>
+      <c r="I17" s="19"/>
+    </row>
+    <row r="18" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="B18" s="11" t="s">
+      <c r="B18" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="C18" s="11" t="s">
+      <c r="C18" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="D18" s="14">
+      <c r="D18" s="10">
         <v>0.875</v>
       </c>
-      <c r="E18" s="14">
+      <c r="E18" s="10">
         <v>0.5</v>
       </c>
-      <c r="F18" s="11"/>
-      <c r="G18" s="16" t="s">
+      <c r="F18" s="8"/>
+      <c r="G18" s="20" t="s">
         <v>136</v>
       </c>
-      <c r="H18" s="11"/>
-      <c r="I18" s="12"/>
-    </row>
-    <row r="19" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="10" t="s">
+      <c r="H18" s="8"/>
+      <c r="I18" s="19"/>
+    </row>
+    <row r="19" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="B19" s="11" t="s">
+      <c r="B19" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="C19" s="11" t="s">
+      <c r="C19" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="D19" s="14">
+      <c r="D19" s="10">
         <v>0.8125</v>
       </c>
-      <c r="E19" s="14">
+      <c r="E19" s="10">
         <v>0.86458333333333337</v>
       </c>
-      <c r="F19" s="11"/>
-      <c r="G19" s="11" t="s">
+      <c r="F19" s="8"/>
+      <c r="G19" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="H19" s="11" t="s">
+      <c r="H19" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="I19" s="12"/>
-    </row>
-    <row r="20" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="10" t="s">
+      <c r="I19" s="19"/>
+    </row>
+    <row r="20" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="B20" s="11" t="s">
+      <c r="B20" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C20" s="11" t="s">
+      <c r="C20" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="D20" s="11" t="s">
+      <c r="D20" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="E20" s="14">
+      <c r="E20" s="10">
         <v>0.79166666666666663</v>
       </c>
-      <c r="F20" s="11"/>
-      <c r="G20" s="16" t="s">
+      <c r="F20" s="8"/>
+      <c r="G20" s="20" t="s">
         <v>129</v>
       </c>
-      <c r="H20" s="11"/>
-      <c r="I20" s="12" t="s">
+      <c r="H20" s="8"/>
+      <c r="I20" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="J20" t="s">
+      <c r="J20" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="K20" t="s">
+      <c r="K20" s="16" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="10" t="s">
+    <row r="21" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="B21" s="11" t="s">
+      <c r="B21" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="C21" s="11"/>
-      <c r="D21" s="11" t="s">
+      <c r="C21" s="8"/>
+      <c r="D21" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="E21" s="11"/>
-      <c r="F21" s="11"/>
-      <c r="G21" s="11"/>
-      <c r="H21" s="11"/>
-      <c r="I21" s="12"/>
-    </row>
-    <row r="22" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="10" t="s">
+      <c r="E21" s="8"/>
+      <c r="F21" s="8"/>
+      <c r="G21" s="8"/>
+      <c r="H21" s="8"/>
+      <c r="I21" s="19"/>
+    </row>
+    <row r="22" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="B22" s="11" t="s">
+      <c r="B22" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="C22" s="11" t="s">
+      <c r="C22" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="D22" s="11" t="s">
+      <c r="D22" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="E22" s="14">
+      <c r="E22" s="10">
         <v>0.75</v>
       </c>
-      <c r="F22" s="11" t="s">
+      <c r="F22" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="G22" s="15" t="s">
+      <c r="G22" s="20" t="s">
         <v>126</v>
       </c>
-      <c r="H22" s="11"/>
-      <c r="I22" s="12"/>
-      <c r="L22" t="s">
+      <c r="H22" s="8"/>
+      <c r="I22" s="19"/>
+      <c r="L22" s="16" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="23" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="10" t="s">
+      <c r="M22" s="16" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="B23" s="11" t="s">
+      <c r="B23" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="C23" s="11" t="s">
+      <c r="C23" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="D23" s="11" t="s">
+      <c r="D23" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="E23" s="14">
+      <c r="E23" s="10">
         <v>0.83333333333333337</v>
       </c>
-      <c r="F23" s="11"/>
-      <c r="G23" s="15" t="s">
+      <c r="F23" s="8"/>
+      <c r="G23" s="20" t="s">
         <v>127</v>
       </c>
-      <c r="H23" s="11"/>
-      <c r="I23" s="12"/>
-      <c r="L23" t="s">
+      <c r="H23" s="8"/>
+      <c r="I23" s="19"/>
+      <c r="L23" s="16" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="24" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="10" t="s">
+    <row r="24" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="B24" s="11" t="s">
+      <c r="B24" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C24" s="11"/>
-      <c r="D24" s="13" t="s">
+      <c r="C24" s="8"/>
+      <c r="D24" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="E24" s="14">
+      <c r="E24" s="10">
         <v>0.75</v>
       </c>
-      <c r="F24" s="11"/>
-      <c r="G24" s="8" t="s">
+      <c r="F24" s="8"/>
+      <c r="G24" s="16" t="s">
         <v>137</v>
       </c>
-      <c r="I24" s="12"/>
-      <c r="L24" s="11" t="s">
+      <c r="I24" s="19"/>
+      <c r="L24" s="8" t="s">
         <v>138</v>
       </c>
     </row>
@@ -1586,16 +1581,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="B1" s="21"/>
+      <c r="B1" s="13"/>
     </row>
     <row r="2" spans="1:2" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="B2" s="21"/>
+      <c r="B2" s="13"/>
     </row>
     <row r="3" spans="1:2" ht="8" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>

--- a/docs/shows/shows.xlsx
+++ b/docs/shows/shows.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/milesshultz/Documents/kings_website/rock/docs/shows/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B7BB4BC-AC33-3D4A-BFCF-7CA5F0EE9F0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F06E40B0-D3EF-084A-B404-D942B473D79A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="140">
   <si>
     <t>HOW TO ADD A SHOW: Fill in a new row below. Date format: YYYY-MM-DD. Start/End Time: H:MM AM/PM (e.g. 7:00 PM). Address: full street address for Maps link (e.g. 1600 Dodge Ave, Evanston, IL 60201). Cancelled: TRUE or FALSE. Leave optional columns blank if not needed. After saving, run:  python docs/shows/update_shows.py  then commit &amp; push.</t>
   </si>
@@ -470,6 +470,9 @@
   </si>
   <si>
     <t>The greatest block party on our street!</t>
+  </si>
+  <si>
+    <t>2027-09-11</t>
   </si>
 </sst>
 </file>
@@ -667,19 +670,6 @@
     <xf numFmtId="18" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -694,6 +684,19 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -997,81 +1000,81 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18" style="16" customWidth="1"/>
-    <col min="2" max="2" width="30.83203125" style="16" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="104.5" style="16" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="35.6640625" style="16" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="37" style="16" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="46.5" style="16" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="43" style="16" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="129.6640625" style="16" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="37" style="16" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="33.5" style="16" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="21.5" style="16" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="118.83203125" style="16" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.83203125" style="16" customWidth="1"/>
-    <col min="14" max="16384" width="8.83203125" style="16"/>
+    <col min="1" max="1" width="18" style="11" customWidth="1"/>
+    <col min="2" max="2" width="30.83203125" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="104.5" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="35.6640625" style="11" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="37" style="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="46.5" style="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="43" style="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="129.6640625" style="11" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="37" style="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="33.5" style="11" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="21.5" style="11" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="118.83203125" style="11" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.83203125" style="11" customWidth="1"/>
+    <col min="14" max="16384" width="8.83203125" style="11"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
     </row>
     <row r="2" spans="1:13" ht="54" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="C2" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="17" t="s">
+      <c r="D2" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="17" t="s">
+      <c r="E2" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="17" t="s">
+      <c r="F2" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="17" t="s">
+      <c r="G2" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="17" t="s">
+      <c r="H2" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="17" t="s">
+      <c r="I2" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="16" t="s">
+      <c r="J2" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="16" t="s">
+      <c r="K2" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="L2" s="16" t="s">
+      <c r="L2" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="M2" s="16" t="s">
+      <c r="M2" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="18" t="s">
+      <c r="A3" s="13" t="s">
         <v>14</v>
       </c>
       <c r="B3" s="8" t="s">
@@ -1085,16 +1088,16 @@
         <v>0.75</v>
       </c>
       <c r="F3" s="8"/>
-      <c r="G3" s="16" t="s">
+      <c r="G3" s="11" t="s">
         <v>137</v>
       </c>
-      <c r="I3" s="19"/>
+      <c r="I3" s="14"/>
       <c r="L3" s="8" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="13" t="s">
         <v>16</v>
       </c>
       <c r="B4" s="8" t="s">
@@ -1108,16 +1111,16 @@
         <v>0.5625</v>
       </c>
       <c r="F4" s="8"/>
-      <c r="G4" s="20" t="s">
+      <c r="G4" s="15" t="s">
         <v>130</v>
       </c>
       <c r="H4" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="I4" s="19"/>
+      <c r="I4" s="14"/>
     </row>
     <row r="5" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="18" t="s">
+      <c r="A5" s="13" t="s">
         <v>19</v>
       </c>
       <c r="B5" s="8" t="s">
@@ -1129,14 +1132,14 @@
       <c r="D5" s="8"/>
       <c r="E5" s="8"/>
       <c r="F5" s="8"/>
-      <c r="G5" s="20" t="s">
+      <c r="G5" s="15" t="s">
         <v>129</v>
       </c>
       <c r="H5" s="8"/>
-      <c r="I5" s="19"/>
+      <c r="I5" s="14"/>
     </row>
     <row r="6" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="18" t="s">
+      <c r="A6" s="13" t="s">
         <v>22</v>
       </c>
       <c r="B6" s="8" t="s">
@@ -1148,14 +1151,14 @@
       <c r="D6" s="8"/>
       <c r="E6" s="8"/>
       <c r="F6" s="8"/>
-      <c r="G6" s="20" t="s">
+      <c r="G6" s="15" t="s">
         <v>131</v>
       </c>
       <c r="H6" s="8"/>
-      <c r="I6" s="19"/>
+      <c r="I6" s="14"/>
     </row>
     <row r="7" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="18" t="s">
+      <c r="A7" s="13" t="s">
         <v>25</v>
       </c>
       <c r="B7" s="8" t="s">
@@ -1166,10 +1169,10 @@
       <c r="E7" s="8"/>
       <c r="F7" s="8"/>
       <c r="H7" s="8"/>
-      <c r="I7" s="19"/>
+      <c r="I7" s="14"/>
     </row>
     <row r="8" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="18" t="s">
+      <c r="A8" s="13" t="s">
         <v>27</v>
       </c>
       <c r="B8" s="8" t="s">
@@ -1181,14 +1184,14 @@
       <c r="D8" s="8"/>
       <c r="E8" s="8"/>
       <c r="F8" s="8"/>
-      <c r="G8" s="20" t="s">
+      <c r="G8" s="15" t="s">
         <v>129</v>
       </c>
       <c r="H8" s="8"/>
-      <c r="I8" s="19"/>
+      <c r="I8" s="14"/>
     </row>
     <row r="9" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="18" t="s">
+      <c r="A9" s="13" t="s">
         <v>28</v>
       </c>
       <c r="B9" s="8" t="s">
@@ -1202,16 +1205,16 @@
         <v>0.75</v>
       </c>
       <c r="F9" s="8"/>
-      <c r="G9" s="16" t="s">
+      <c r="G9" s="11" t="s">
         <v>137</v>
       </c>
-      <c r="I9" s="19"/>
+      <c r="I9" s="14"/>
       <c r="L9" s="8" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="18" t="s">
+      <c r="A10" s="13" t="s">
         <v>29</v>
       </c>
       <c r="B10" s="8" t="s">
@@ -1223,22 +1226,22 @@
       <c r="D10" s="8"/>
       <c r="E10" s="8"/>
       <c r="F10" s="8"/>
-      <c r="G10" s="20" t="s">
+      <c r="G10" s="15" t="s">
         <v>129</v>
       </c>
       <c r="H10" s="8"/>
-      <c r="I10" s="19" t="s">
+      <c r="I10" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="J10" s="16" t="s">
+      <c r="J10" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="K10" s="16" t="s">
+      <c r="K10" s="11" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="18" t="s">
+      <c r="A11" s="13" t="s">
         <v>33</v>
       </c>
       <c r="B11" s="8" t="s">
@@ -1252,16 +1255,16 @@
         <v>0.5625</v>
       </c>
       <c r="F11" s="8"/>
-      <c r="G11" s="20" t="s">
+      <c r="G11" s="15" t="s">
         <v>130</v>
       </c>
       <c r="H11" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="I11" s="19"/>
+      <c r="I11" s="14"/>
     </row>
     <row r="12" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="18" t="s">
+      <c r="A12" s="13" t="s">
         <v>34</v>
       </c>
       <c r="B12" s="8" t="s">
@@ -1273,14 +1276,14 @@
       <c r="D12" s="8"/>
       <c r="E12" s="8"/>
       <c r="F12" s="8"/>
-      <c r="G12" s="20" t="s">
+      <c r="G12" s="15" t="s">
         <v>129</v>
       </c>
       <c r="H12" s="8"/>
-      <c r="I12" s="19"/>
+      <c r="I12" s="14"/>
     </row>
     <row r="13" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="18" t="s">
+      <c r="A13" s="13" t="s">
         <v>35</v>
       </c>
       <c r="B13" s="8" t="s">
@@ -1296,10 +1299,10 @@
         <v>132</v>
       </c>
       <c r="H13" s="8"/>
-      <c r="I13" s="19"/>
+      <c r="I13" s="14"/>
     </row>
     <row r="14" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="18" t="s">
+      <c r="A14" s="13" t="s">
         <v>38</v>
       </c>
       <c r="B14" s="8" t="s">
@@ -1309,17 +1312,17 @@
       <c r="D14" s="8"/>
       <c r="E14" s="8"/>
       <c r="F14" s="8"/>
-      <c r="G14" s="16" t="s">
+      <c r="G14" s="11" t="s">
         <v>137</v>
       </c>
       <c r="H14" s="8"/>
-      <c r="I14" s="19"/>
+      <c r="I14" s="14"/>
       <c r="L14" s="8" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="18" t="s">
+      <c r="A15" s="13" t="s">
         <v>39</v>
       </c>
       <c r="B15" s="8" t="s">
@@ -1333,15 +1336,15 @@
         <v>133</v>
       </c>
       <c r="H15" s="8"/>
-      <c r="I15" s="19" t="s">
+      <c r="I15" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="J15" s="16" t="s">
+      <c r="J15" s="11" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="18" t="s">
+      <c r="A16" s="13" t="s">
         <v>43</v>
       </c>
       <c r="B16" s="8" t="s">
@@ -1353,19 +1356,19 @@
       <c r="D16" s="8"/>
       <c r="E16" s="8"/>
       <c r="F16" s="8"/>
-      <c r="G16" s="20" t="s">
+      <c r="G16" s="15" t="s">
         <v>134</v>
       </c>
       <c r="H16" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="I16" s="19"/>
-      <c r="M16" s="16" t="s">
+      <c r="I16" s="14"/>
+      <c r="M16" s="11" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="18" t="s">
+      <c r="A17" s="13" t="s">
         <v>48</v>
       </c>
       <c r="B17" s="8" t="s">
@@ -1381,14 +1384,14 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="F17" s="8"/>
-      <c r="G17" s="20" t="s">
+      <c r="G17" s="15" t="s">
         <v>135</v>
       </c>
       <c r="H17" s="8"/>
-      <c r="I17" s="19"/>
+      <c r="I17" s="14"/>
     </row>
     <row r="18" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="18" t="s">
+      <c r="A18" s="13" t="s">
         <v>51</v>
       </c>
       <c r="B18" s="8" t="s">
@@ -1404,14 +1407,14 @@
         <v>0.5</v>
       </c>
       <c r="F18" s="8"/>
-      <c r="G18" s="20" t="s">
+      <c r="G18" s="15" t="s">
         <v>136</v>
       </c>
       <c r="H18" s="8"/>
-      <c r="I18" s="19"/>
+      <c r="I18" s="14"/>
     </row>
     <row r="19" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="18" t="s">
+      <c r="A19" s="13" t="s">
         <v>54</v>
       </c>
       <c r="B19" s="8" t="s">
@@ -1433,10 +1436,10 @@
       <c r="H19" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="I19" s="19"/>
+      <c r="I19" s="14"/>
     </row>
     <row r="20" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="18" t="s">
+      <c r="A20" s="13" t="s">
         <v>56</v>
       </c>
       <c r="B20" s="8" t="s">
@@ -1452,22 +1455,22 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="F20" s="8"/>
-      <c r="G20" s="20" t="s">
+      <c r="G20" s="15" t="s">
         <v>129</v>
       </c>
       <c r="H20" s="8"/>
-      <c r="I20" s="19" t="s">
+      <c r="I20" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="J20" s="16" t="s">
+      <c r="J20" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="K20" s="16" t="s">
+      <c r="K20" s="11" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="18" t="s">
+      <c r="A21" s="13" t="s">
         <v>58</v>
       </c>
       <c r="B21" s="8" t="s">
@@ -1481,10 +1484,10 @@
       <c r="F21" s="8"/>
       <c r="G21" s="8"/>
       <c r="H21" s="8"/>
-      <c r="I21" s="19"/>
+      <c r="I21" s="14"/>
     </row>
     <row r="22" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="18" t="s">
+      <c r="A22" s="13" t="s">
         <v>60</v>
       </c>
       <c r="B22" s="8" t="s">
@@ -1502,20 +1505,20 @@
       <c r="F22" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="G22" s="20" t="s">
+      <c r="G22" s="15" t="s">
         <v>126</v>
       </c>
       <c r="H22" s="8"/>
-      <c r="I22" s="19"/>
-      <c r="L22" s="16" t="s">
+      <c r="I22" s="14"/>
+      <c r="L22" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="M22" s="16" t="b">
+      <c r="M22" s="11" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="18" t="s">
+      <c r="A23" s="13" t="s">
         <v>63</v>
       </c>
       <c r="B23" s="8" t="s">
@@ -1531,17 +1534,17 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="F23" s="8"/>
-      <c r="G23" s="20" t="s">
+      <c r="G23" s="15" t="s">
         <v>127</v>
       </c>
       <c r="H23" s="8"/>
-      <c r="I23" s="19"/>
-      <c r="L23" s="16" t="s">
+      <c r="I23" s="14"/>
+      <c r="L23" s="11" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="18" t="s">
+      <c r="A24" s="13" t="s">
         <v>68</v>
       </c>
       <c r="B24" s="8" t="s">
@@ -1555,11 +1558,34 @@
         <v>0.75</v>
       </c>
       <c r="F24" s="8"/>
-      <c r="G24" s="16" t="s">
+      <c r="G24" s="11" t="s">
         <v>137</v>
       </c>
-      <c r="I24" s="19"/>
+      <c r="I24" s="14"/>
       <c r="L24" s="8" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C25" s="8"/>
+      <c r="D25" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="E25" s="10">
+        <v>0.75</v>
+      </c>
+      <c r="F25" s="8"/>
+      <c r="G25" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="I25" s="14"/>
+      <c r="L25" s="8" t="s">
         <v>138</v>
       </c>
     </row>
@@ -1581,16 +1607,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="B1" s="13"/>
+      <c r="B1" s="19"/>
     </row>
     <row r="2" spans="1:2" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="B2" s="13"/>
+      <c r="B2" s="19"/>
     </row>
     <row r="3" spans="1:2" ht="8" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>

--- a/docs/shows/shows.xlsx
+++ b/docs/shows/shows.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/milesshultz/Documents/kings_website/rock/docs/shows/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F06E40B0-D3EF-084A-B404-D942B473D79A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F013A5A5-E2E7-6146-BED8-A7A9907BED9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -469,10 +469,10 @@
     <t>Ewing Ave &amp; Payne St, Evanston, IL 60201</t>
   </si>
   <si>
-    <t>The greatest block party on our street!</t>
-  </si>
-  <si>
     <t>2027-09-11</t>
+  </si>
+  <si>
+    <t>The party that accidentally started a band.</t>
   </si>
 </sst>
 </file>
@@ -1032,7 +1032,7 @@
       <c r="H1" s="17"/>
       <c r="I1" s="17"/>
     </row>
-    <row r="2" spans="1:13" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" ht="54" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
         <v>1</v>
       </c>
@@ -1092,8 +1092,8 @@
         <v>137</v>
       </c>
       <c r="I3" s="14"/>
-      <c r="L3" s="8" t="s">
-        <v>138</v>
+      <c r="L3" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
@@ -1209,8 +1209,8 @@
         <v>137</v>
       </c>
       <c r="I9" s="14"/>
-      <c r="L9" s="8" t="s">
-        <v>138</v>
+      <c r="L9" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
@@ -1317,8 +1317,8 @@
       </c>
       <c r="H14" s="8"/>
       <c r="I14" s="14"/>
-      <c r="L14" s="8" t="s">
-        <v>138</v>
+      <c r="L14" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
@@ -1562,13 +1562,13 @@
         <v>137</v>
       </c>
       <c r="I24" s="14"/>
-      <c r="L24" s="8" t="s">
-        <v>138</v>
+      <c r="L24" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="13" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B25" s="8" t="s">
         <v>15</v>
@@ -1585,8 +1585,8 @@
         <v>137</v>
       </c>
       <c r="I25" s="14"/>
-      <c r="L25" s="8" t="s">
-        <v>138</v>
+      <c r="L25" t="s">
+        <v>139</v>
       </c>
     </row>
   </sheetData>

--- a/docs/shows/shows.xlsx
+++ b/docs/shows/shows.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10621"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/milesshultz/Documents/kings_website/rock/docs/shows/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC443323-162C-A447-B01B-429A43BF0A6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64CFBEF2-8A23-C74A-9FF3-612B706D2BE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1704,6 +1704,9 @@
       <c r="L24" s="11" t="s">
         <v>82</v>
       </c>
+      <c r="M24" s="11" t="b">
+        <v>1</v>
+      </c>
       <c r="P24" s="11" t="s">
         <v>164</v>
       </c>
